--- a/etf_holdings/2026-10-01_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-01_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:11</t>
+          <t>2026-10-01 23:31:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:12</t>
+          <t>2026-10-01 23:31:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:14</t>
+          <t>2026-10-01 23:32:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:15</t>
+          <t>2026-10-01 23:32:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:20</t>
+          <t>2026-10-01 23:32:07</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:21</t>
+          <t>2026-10-01 23:32:08</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:22</t>
+          <t>2026-10-01 23:32:10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:24</t>
+          <t>2026-10-01 23:32:11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:24</t>
+          <t>2026-10-01 23:32:11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:24</t>
+          <t>2026-10-01 23:32:11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:24</t>
+          <t>2026-10-01 23:32:11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:24</t>
+          <t>2026-10-01 23:32:11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:28</t>
+          <t>2026-10-01 23:32:16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:30</t>
+          <t>2026-10-01 23:32:18</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:31</t>
+          <t>2026-10-01 23:32:19</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:32</t>
+          <t>2026-10-01 23:32:20</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:32</t>
+          <t>2026-10-01 23:32:20</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:32</t>
+          <t>2026-10-01 23:32:20</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:32</t>
+          <t>2026-10-01 23:32:20</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:32</t>
+          <t>2026-10-01 23:32:20</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:37</t>
+          <t>2026-10-01 23:32:29</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:38</t>
+          <t>2026-10-01 23:32:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:40</t>
+          <t>2026-10-01 23:32:31</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:41</t>
+          <t>2026-10-01 23:32:32</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:46</t>
+          <t>2026-10-01 23:32:38</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:49</t>
+          <t>2026-10-01 23:32:40</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:50</t>
+          <t>2026-10-01 23:32:41</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:51</t>
+          <t>2026-10-01 23:32:42</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:51</t>
+          <t>2026-10-01 23:32:42</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:51</t>
+          <t>2026-10-01 23:32:42</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:51</t>
+          <t>2026-10-01 23:32:42</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:51</t>
+          <t>2026-10-01 23:32:42</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:56</t>
+          <t>2026-10-01 23:32:48</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:57</t>
+          <t>2026-10-01 23:32:49</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-01 19:25:59</t>
+          <t>2026-10-01 23:32:50</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:00</t>
+          <t>2026-10-01 23:32:51</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:00</t>
+          <t>2026-10-01 23:32:51</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:00</t>
+          <t>2026-10-01 23:32:51</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:00</t>
+          <t>2026-10-01 23:32:51</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:00</t>
+          <t>2026-10-01 23:32:51</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:07</t>
+          <t>2026-10-01 23:32:57</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:08</t>
+          <t>2026-10-01 23:32:58</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:10</t>
+          <t>2026-10-01 23:33:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:15</t>
+          <t>2026-10-01 23:33:05</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:15</t>
+          <t>2026-10-01 23:33:05</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:15</t>
+          <t>2026-10-01 23:33:05</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:17</t>
+          <t>2026-10-01 23:33:06</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22375,7 +22375,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:18</t>
+          <t>2026-10-01 23:33:08</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:25</t>
+          <t>2026-10-01 23:33:14</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:27</t>
+          <t>2026-10-01 23:33:16</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:28</t>
+          <t>2026-10-01 23:33:17</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:35</t>
+          <t>2026-10-01 23:33:34</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:36</t>
+          <t>2026-10-01 23:33:35</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:38</t>
+          <t>2026-10-01 23:33:36</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:39</t>
+          <t>2026-10-01 23:33:38</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:39</t>
+          <t>2026-10-01 23:33:38</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:39</t>
+          <t>2026-10-01 23:33:38</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:39</t>
+          <t>2026-10-01 23:33:38</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:39</t>
+          <t>2026-10-01 23:33:38</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:44</t>
+          <t>2026-10-01 23:33:45</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:45</t>
+          <t>2026-10-01 23:33:46</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:46</t>
+          <t>2026-10-01 23:33:47</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:47</t>
+          <t>2026-10-01 23:33:49</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:52</t>
+          <t>2026-10-01 23:33:55</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:54</t>
+          <t>2026-10-01 23:33:56</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-10-01 19:26:56</t>
+          <t>2026-10-01 23:33:57</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">

--- a/etf_holdings/2026-10-01_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-01_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:58</t>
+          <t>2026-10-01 23:40:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-01 23:31:59</t>
+          <t>2026-10-01 23:40:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:00</t>
+          <t>2026-10-01 23:40:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:01</t>
+          <t>2026-10-01 23:40:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:07</t>
+          <t>2026-10-01 23:40:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:08</t>
+          <t>2026-10-01 23:40:17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:10</t>
+          <t>2026-10-01 23:40:18</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:11</t>
+          <t>2026-10-01 23:40:19</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:11</t>
+          <t>2026-10-01 23:40:19</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:11</t>
+          <t>2026-10-01 23:40:19</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:11</t>
+          <t>2026-10-01 23:40:19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:11</t>
+          <t>2026-10-01 23:40:19</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:16</t>
+          <t>2026-10-01 23:40:24</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:18</t>
+          <t>2026-10-01 23:40:26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:19</t>
+          <t>2026-10-01 23:40:27</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:20</t>
+          <t>2026-10-01 23:40:28</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:20</t>
+          <t>2026-10-01 23:40:28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:20</t>
+          <t>2026-10-01 23:40:28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:20</t>
+          <t>2026-10-01 23:40:28</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:20</t>
+          <t>2026-10-01 23:40:28</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:29</t>
+          <t>2026-10-01 23:40:33</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:30</t>
+          <t>2026-10-01 23:40:34</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:31</t>
+          <t>2026-10-01 23:40:35</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:32</t>
+          <t>2026-10-01 23:40:37</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:38</t>
+          <t>2026-10-01 23:40:41</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:40</t>
+          <t>2026-10-01 23:40:43</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:41</t>
+          <t>2026-10-01 23:40:44</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:42</t>
+          <t>2026-10-01 23:40:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:42</t>
+          <t>2026-10-01 23:40:45</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:42</t>
+          <t>2026-10-01 23:40:45</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:42</t>
+          <t>2026-10-01 23:40:45</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:42</t>
+          <t>2026-10-01 23:40:45</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:48</t>
+          <t>2026-10-01 23:40:50</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:49</t>
+          <t>2026-10-01 23:40:52</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:50</t>
+          <t>2026-10-01 23:40:53</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:51</t>
+          <t>2026-10-01 23:40:54</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:51</t>
+          <t>2026-10-01 23:40:54</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:51</t>
+          <t>2026-10-01 23:40:54</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:51</t>
+          <t>2026-10-01 23:40:54</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:51</t>
+          <t>2026-10-01 23:40:54</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19551,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:57</t>
+          <t>2026-10-01 23:41:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20527,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-01 23:32:58</t>
+          <t>2026-10-01 23:41:02</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:00</t>
+          <t>2026-10-01 23:41:03</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:05</t>
+          <t>2026-10-01 23:41:08</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:05</t>
+          <t>2026-10-01 23:41:08</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:05</t>
+          <t>2026-10-01 23:41:08</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22060,7 +22060,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:06</t>
+          <t>2026-10-01 23:41:09</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22375,7 +22375,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:08</t>
+          <t>2026-10-01 23:41:10</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:14</t>
+          <t>2026-10-01 23:41:17</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:16</t>
+          <t>2026-10-01 23:41:19</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:17</t>
+          <t>2026-10-01 23:41:20</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:34</t>
+          <t>2026-10-01 23:41:26</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:35</t>
+          <t>2026-10-01 23:41:27</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:36</t>
+          <t>2026-10-01 23:41:29</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:38</t>
+          <t>2026-10-01 23:41:30</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:38</t>
+          <t>2026-10-01 23:41:30</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:38</t>
+          <t>2026-10-01 23:41:30</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:38</t>
+          <t>2026-10-01 23:41:30</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:38</t>
+          <t>2026-10-01 23:41:30</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:45</t>
+          <t>2026-10-01 23:41:53</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:46</t>
+          <t>2026-10-01 23:41:54</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:47</t>
+          <t>2026-10-01 23:41:55</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:49</t>
+          <t>2026-10-01 23:41:56</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:55</t>
+          <t>2026-10-01 23:42:02</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:56</t>
+          <t>2026-10-01 23:42:03</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-10-01 23:33:57</t>
+          <t>2026-10-01 23:42:04</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
